--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -62863,6 +62863,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>82000</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -62796,10 +62796,10 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C2715" t="n">
         <v>0.654999971389771</v>
@@ -62819,10 +62819,10 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C2716" t="n">
         <v>0.654999971389771</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>0</v>
@@ -62865,7 +62865,7 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
         <v>0</v>
@@ -62888,10 +62888,10 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C2719" t="n">
         <v>0.654999971389771</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.665000021457672</v>
+        <v>0.654999971389771</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.649999976158142</v>
+        <v>0.654999971389771</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.665000021457672</v>
+        <v>0.654999971389771</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.649999976158142</v>
+        <v>0.654999971389771</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>82000</v>
+        <v>19000</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.634999990463257</v>
+        <v>0.665000021457672</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.560000002384186</v>
+        <v>0.649999976158142</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.634999990463257</v>
+        <v>0.665000021457672</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.584999978542328</v>
+        <v>0.649999976158142</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3000</v>
+        <v>82000</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.589999973773956</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.579999983310699</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.589999973773956</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.579999983310699</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63070,6 +63070,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="G2727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63139,6 +63139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63162,6 +63162,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2731">
+      <c r="A2731" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2731" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2731" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2731" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63185,6 +63185,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63208,6 +63208,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2733">
+      <c r="A2733" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2733" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2733" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63231,6 +63231,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2734" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63254,6 +63254,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.555000007152557</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.545000016689301</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63316,7 +63316,9 @@
       <c r="E2737" t="n">
         <v>0.564999997615814</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.564999997615814</v>
+      </c>
       <c r="G2737" t="s">
         <v>7</v>
       </c>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63323,6 +63323,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63415,6 +63415,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2742">
+      <c r="A2742" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2742" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2742" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2742" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G2742" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -63438,6 +63438,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G2743" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NRST.MI.xlsx
+++ b/data/NRST.MI.xlsx
@@ -80157,6 +80157,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
